--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008524561436371531</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>47888662</v>
+        <v>3998370</v>
       </c>
       <c r="L2" t="n">
-        <v>25260348</v>
+        <v>1673259</v>
       </c>
       <c r="M2" t="n">
-        <v>5657403</v>
+        <v>284466</v>
       </c>
       <c r="N2" t="n">
-        <v>245319</v>
+        <v>5561</v>
       </c>
       <c r="O2" t="n">
-        <v>3309507</v>
+        <v>149503</v>
       </c>
       <c r="P2" t="n">
-        <v>1256526</v>
+        <v>52164</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999027252197266</v>
+        <v>0.9996587634086609</v>
       </c>
       <c r="R2" t="n">
-        <v>0.831651508808136</v>
+        <v>0.7143740057945251</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7005226016044617</v>
+        <v>0.5313200354576111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6364351511001587</v>
+        <v>0.4016253352165222</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1981032639741898</v>
+        <v>0.04134019091725349</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6842700242996216</v>
+        <v>0.4453271329402924</v>
       </c>
       <c r="W2" t="n">
-        <v>0.800286591053009</v>
+        <v>0.5817200541496277</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00204248073217291</v>
       </c>
       <c r="C3" t="n">
-        <v>759</v>
+        <v>259</v>
       </c>
       <c r="D3" t="n">
-        <v>47888662</v>
+        <v>3998370</v>
       </c>
       <c r="E3" t="n">
-        <v>6918094</v>
+        <v>903594</v>
       </c>
       <c r="F3" t="n">
-        <v>182133</v>
+        <v>35044</v>
       </c>
       <c r="G3" t="n">
-        <v>17726</v>
+        <v>3489</v>
       </c>
       <c r="H3" t="n">
-        <v>11192</v>
+        <v>2773</v>
       </c>
       <c r="I3" t="n">
-        <v>1130</v>
+        <v>427</v>
       </c>
       <c r="J3" t="n">
-        <v>110176088</v>
+        <v>10014467</v>
       </c>
       <c r="K3" t="n">
-        <v>114911958</v>
+        <v>9786988</v>
       </c>
       <c r="L3" t="n">
-        <v>132684824</v>
+        <v>11521095</v>
       </c>
       <c r="M3" t="n">
-        <v>166097488</v>
+        <v>14962023</v>
       </c>
       <c r="N3" t="n">
-        <v>177649056</v>
+        <v>16110683</v>
       </c>
       <c r="O3" t="n">
-        <v>172485623</v>
+        <v>15630885</v>
       </c>
       <c r="P3" t="n">
-        <v>177183486</v>
+        <v>16098160</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8703912496566772</v>
+        <v>0.8087390065193176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6989226937294006</v>
+        <v>0.502100944519043</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5494593381881714</v>
+        <v>0.3014190196990967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2494285851716995</v>
+        <v>0.06181636452674866</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5896216630935669</v>
+        <v>0.2917114496231079</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5903215408325195</v>
+        <v>0.2689808905124664</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03218358813514684</v>
       </c>
       <c r="C4" t="n">
-        <v>330</v>
+        <v>140</v>
       </c>
       <c r="D4" t="n">
-        <v>8923660</v>
+        <v>1424063</v>
       </c>
       <c r="E4" t="n">
-        <v>25260348</v>
+        <v>1673259</v>
       </c>
       <c r="F4" t="n">
-        <v>1642878</v>
+        <v>183198</v>
       </c>
       <c r="G4" t="n">
-        <v>121918</v>
+        <v>19568</v>
       </c>
       <c r="H4" t="n">
-        <v>173377</v>
+        <v>28051</v>
       </c>
       <c r="I4" t="n">
-        <v>19324</v>
+        <v>4236</v>
       </c>
       <c r="J4" t="n">
-        <v>6754</v>
+        <v>2155</v>
       </c>
       <c r="K4" t="n">
-        <v>9693946</v>
+        <v>1598656</v>
       </c>
       <c r="L4" t="n">
-        <v>10798941</v>
+        <v>1475990</v>
       </c>
       <c r="M4" t="n">
-        <v>3231803</v>
+        <v>423821</v>
       </c>
       <c r="N4" t="n">
-        <v>993020</v>
+        <v>128957</v>
       </c>
       <c r="O4" t="n">
-        <v>1527044</v>
+        <v>186212</v>
       </c>
       <c r="P4" t="n">
-        <v>313569</v>
+        <v>37508</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999513626098633</v>
+        <v>0.9998293519020081</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8505804538726807</v>
+        <v>0.7586332559585571</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6997217535972595</v>
+        <v>0.5162973999977112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5897577404975891</v>
+        <v>0.3443808853626251</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2208227962255478</v>
+        <v>0.04954605922102928</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6334297657012939</v>
+        <v>0.3525107800960541</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6794530153274536</v>
+        <v>0.3678650557994843</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1086</v>
+        <v>399</v>
       </c>
       <c r="D5" t="n">
-        <v>551440</v>
+        <v>128763</v>
       </c>
       <c r="E5" t="n">
-        <v>3112335</v>
+        <v>422207</v>
       </c>
       <c r="F5" t="n">
-        <v>5657403</v>
+        <v>284466</v>
       </c>
       <c r="G5" t="n">
-        <v>298462</v>
+        <v>33284</v>
       </c>
       <c r="H5" t="n">
-        <v>606183</v>
+        <v>63185</v>
       </c>
       <c r="I5" t="n">
-        <v>69400</v>
+        <v>11452</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7131034</v>
+        <v>945586</v>
       </c>
       <c r="L5" t="n">
-        <v>10881487</v>
+        <v>1659256</v>
       </c>
       <c r="M5" t="n">
-        <v>4638906</v>
+        <v>659290</v>
       </c>
       <c r="N5" t="n">
-        <v>738205</v>
+        <v>84399</v>
       </c>
       <c r="O5" t="n">
-        <v>2303426</v>
+        <v>363000</v>
       </c>
       <c r="P5" t="n">
-        <v>872019</v>
+        <v>141768</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999623894691467</v>
+        <v>0.9998680353164673</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9063330888748169</v>
+        <v>0.8441944718360901</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8793021440505981</v>
+        <v>0.8080022931098938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9561827182769775</v>
+        <v>0.9336718916893005</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9903620481491089</v>
+        <v>0.9869344234466553</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9786752462387085</v>
+        <v>0.9663670659065247</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9933996796607971</v>
+        <v>0.9890214204788208</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>186</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>159355</v>
+        <v>24038</v>
       </c>
       <c r="E6" t="n">
-        <v>250824</v>
+        <v>28257</v>
       </c>
       <c r="F6" t="n">
-        <v>230535</v>
+        <v>24043</v>
       </c>
       <c r="G6" t="n">
-        <v>245319</v>
+        <v>5561</v>
       </c>
       <c r="H6" t="n">
-        <v>88061</v>
+        <v>6952</v>
       </c>
       <c r="I6" t="n">
-        <v>9244</v>
+        <v>1054</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1552</v>
+        <v>526</v>
       </c>
       <c r="D7" t="n">
-        <v>55202</v>
+        <v>19819</v>
       </c>
       <c r="E7" t="n">
-        <v>471743</v>
+        <v>108774</v>
       </c>
       <c r="F7" t="n">
-        <v>1074835</v>
+        <v>155831</v>
       </c>
       <c r="G7" t="n">
-        <v>485623</v>
+        <v>57711</v>
       </c>
       <c r="H7" t="n">
-        <v>3309507</v>
+        <v>149503</v>
       </c>
       <c r="I7" t="n">
-        <v>214471</v>
+        <v>20339</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2841</v>
+        <v>776</v>
       </c>
       <c r="D8" t="n">
-        <v>4289</v>
+        <v>1973</v>
       </c>
       <c r="E8" t="n">
-        <v>45945</v>
+        <v>13158</v>
       </c>
       <c r="F8" t="n">
-        <v>101422</v>
+        <v>25705</v>
       </c>
       <c r="G8" t="n">
-        <v>69291</v>
+        <v>14905</v>
       </c>
       <c r="H8" t="n">
-        <v>648231</v>
+        <v>85251</v>
       </c>
       <c r="I8" t="n">
-        <v>1256526</v>
+        <v>52164</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
